--- a/系統分析/範本/yyyy年REMOC年度報表(1-MM月)_yyyyMMdd_hhmm.xlsx
+++ b/系統分析/範本/yyyy年REMOC年度報表(1-MM月)_yyyyMMdd_hhmm.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="6370" windowHeight="3940" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="6370" windowHeight="3940"/>
   </bookViews>
   <sheets>
     <sheet name="總表" sheetId="1" r:id="rId1"/>
@@ -643,203 +643,95 @@
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C4" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D4" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E4" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F4" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G4" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C5" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D5" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E5" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F5" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G5" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C6" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D6" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E6" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F6" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G6" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C7" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D7" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E7" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F7" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G7" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C8" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D8" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E8" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F8" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G8" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C9" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D9" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E9" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F9" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G9" s="2" t="e">
-        <f>#REF!</f>
-        <v>#REF!</v>
-      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="e">
+      <c r="B10" s="3">
         <f>SUM(B4:B9)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C10" s="3" t="e">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3">
         <f t="shared" ref="C10:G10" si="0">SUM(C4:C9)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D10" s="3" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="E10" s="3" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="F10" s="3" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="G10" s="3" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1050,27 +942,27 @@
         <v>9</v>
       </c>
       <c r="B16" s="3">
-        <f>SUM(B8:B15)</f>
+        <f t="shared" ref="B16:G16" si="0">SUM(B8:B15)</f>
         <v>0</v>
       </c>
       <c r="C16" s="3">
-        <f>SUM(C8:C15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D16" s="3">
-        <f>SUM(D8:D15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E16" s="3">
-        <f>SUM(E8:E15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <f>SUM(F8:F15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G16" s="3">
-        <f>SUM(G8:G15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1282,27 +1174,27 @@
         <v>9</v>
       </c>
       <c r="B16" s="3">
-        <f>SUM(B8:B15)</f>
+        <f t="shared" ref="B16:G16" si="0">SUM(B8:B15)</f>
         <v>0</v>
       </c>
       <c r="C16" s="3">
-        <f>SUM(C8:C15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D16" s="3">
-        <f>SUM(D8:D15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E16" s="3">
-        <f>SUM(E8:E15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <f>SUM(F8:F15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G16" s="3">
-        <f>SUM(G8:G15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1514,27 +1406,27 @@
         <v>9</v>
       </c>
       <c r="B16" s="3">
-        <f>SUM(B8:B15)</f>
+        <f t="shared" ref="B16:G16" si="0">SUM(B8:B15)</f>
         <v>0</v>
       </c>
       <c r="C16" s="3">
-        <f>SUM(C8:C15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D16" s="3">
-        <f>SUM(D8:D15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E16" s="3">
-        <f>SUM(E8:E15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <f>SUM(F8:F15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G16" s="3">
-        <f>SUM(G8:G15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1746,27 +1638,27 @@
         <v>9</v>
       </c>
       <c r="B16" s="3">
-        <f>SUM(B8:B15)</f>
+        <f t="shared" ref="B16:G16" si="0">SUM(B8:B15)</f>
         <v>0</v>
       </c>
       <c r="C16" s="3">
-        <f>SUM(C8:C15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D16" s="3">
-        <f>SUM(D8:D15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E16" s="3">
-        <f>SUM(E8:E15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <f>SUM(F8:F15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G16" s="3">
-        <f>SUM(G8:G15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -1978,27 +1870,27 @@
         <v>9</v>
       </c>
       <c r="B16" s="3">
-        <f>SUM(B8:B15)</f>
+        <f t="shared" ref="B16:G16" si="0">SUM(B8:B15)</f>
         <v>0</v>
       </c>
       <c r="C16" s="3">
-        <f>SUM(C8:C15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D16" s="3">
-        <f>SUM(D8:D15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E16" s="3">
-        <f>SUM(E8:E15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <f>SUM(F8:F15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G16" s="3">
-        <f>SUM(G8:G15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2210,27 +2102,27 @@
         <v>9</v>
       </c>
       <c r="B16" s="3">
-        <f>SUM(B8:B15)</f>
+        <f t="shared" ref="B16:G16" si="0">SUM(B8:B15)</f>
         <v>0</v>
       </c>
       <c r="C16" s="3">
-        <f>SUM(C8:C15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D16" s="3">
-        <f>SUM(D8:D15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E16" s="3">
-        <f>SUM(E8:E15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <f>SUM(F8:F15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G16" s="3">
-        <f>SUM(G8:G15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2442,27 +2334,27 @@
         <v>9</v>
       </c>
       <c r="B16" s="3">
-        <f>SUM(B8:B15)</f>
+        <f t="shared" ref="B16:G16" si="0">SUM(B8:B15)</f>
         <v>0</v>
       </c>
       <c r="C16" s="3">
-        <f>SUM(C8:C15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="D16" s="3">
-        <f>SUM(D8:D15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E16" s="3">
-        <f>SUM(E8:E15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <f>SUM(F8:F15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G16" s="3">
-        <f>SUM(G8:G15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
